--- a/data/mpi_2024_input.xlsx
+++ b/data/mpi_2024_input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshuasamuel/Documents/GitHub/MPI/risk_engines/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshuasamuel/Documents/GitHub/MPI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296E6F63-ED59-394A-B87D-A90F1EB48B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B536649C-09AF-C84C-933D-E1AF7BCE5BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5600" yWindow="2300" windowWidth="27580" windowHeight="16940" xr2:uid="{8D0C2F2B-6F44-EB49-A1FC-82A6E2BE5C4D}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3885" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="733">
   <si>
     <t>Unique ID</t>
   </si>
@@ -2292,6 +2292,12 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>indigenous_flag_overlay</t>
+  </si>
+  <si>
+    <t>mpo_flag</t>
   </si>
 </sst>
 </file>
@@ -2662,7 +2668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85BF2B2-D70C-FE48-8575-7294DE477936}">
-  <dimension ref="A1:V365"/>
+  <dimension ref="A1:X365"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.796875" customWidth="1"/>
@@ -2682,7 +2688,7 @@
     <col min="20" max="20" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2749,8 +2755,14 @@
       <c r="V1" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W1" t="s">
+        <v>731</v>
+      </c>
+      <c r="X1" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2817,8 +2829,14 @@
       <c r="V2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>10</v>
       </c>
@@ -2885,8 +2903,14 @@
       <c r="V3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>21</v>
       </c>
@@ -2953,8 +2977,14 @@
       <c r="V4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>22</v>
       </c>
@@ -3021,8 +3051,14 @@
       <c r="V5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>76</v>
       </c>
@@ -3089,8 +3125,14 @@
       <c r="V6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>88</v>
       </c>
@@ -3157,8 +3199,14 @@
       <c r="V7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>89</v>
       </c>
@@ -3225,8 +3273,14 @@
       <c r="V8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>92</v>
       </c>
@@ -3293,8 +3347,14 @@
       <c r="V9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>94</v>
       </c>
@@ -3361,8 +3421,14 @@
       <c r="V10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>98</v>
       </c>
@@ -3429,8 +3495,14 @@
       <c r="V11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>100</v>
       </c>
@@ -3497,8 +3569,14 @@
       <c r="V12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>114</v>
       </c>
@@ -3565,8 +3643,14 @@
       <c r="V13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>126</v>
       </c>
@@ -3633,8 +3717,14 @@
       <c r="V14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>130</v>
       </c>
@@ -3701,8 +3791,14 @@
       <c r="V15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>140</v>
       </c>
@@ -3769,8 +3865,14 @@
       <c r="V16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>165</v>
       </c>
@@ -3837,8 +3939,14 @@
       <c r="V17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>186</v>
       </c>
@@ -3905,8 +4013,14 @@
       <c r="V18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>188</v>
       </c>
@@ -3973,8 +4087,14 @@
       <c r="V19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>205</v>
       </c>
@@ -4041,8 +4161,14 @@
       <c r="V20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>207</v>
       </c>
@@ -4109,8 +4235,14 @@
       <c r="V21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>209</v>
       </c>
@@ -4177,8 +4309,14 @@
       <c r="V22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>238</v>
       </c>
@@ -4245,8 +4383,14 @@
       <c r="V23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>256</v>
       </c>
@@ -4313,8 +4457,14 @@
       <c r="V24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>283</v>
       </c>
@@ -4381,8 +4531,14 @@
       <c r="V25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>314</v>
       </c>
@@ -4449,8 +4605,14 @@
       <c r="V26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W26">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>329</v>
       </c>
@@ -4517,8 +4679,14 @@
       <c r="V27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W27">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>341</v>
       </c>
@@ -4585,8 +4753,14 @@
       <c r="V28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W28">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>344</v>
       </c>
@@ -4653,8 +4827,14 @@
       <c r="V29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W29">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>371</v>
       </c>
@@ -4721,8 +4901,14 @@
       <c r="V30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W30">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>376</v>
       </c>
@@ -4789,8 +4975,14 @@
       <c r="V31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>390</v>
       </c>
@@ -4857,8 +5049,14 @@
       <c r="V32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W32">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>399</v>
       </c>
@@ -4925,8 +5123,14 @@
       <c r="V33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W33">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>404</v>
       </c>
@@ -4993,8 +5197,14 @@
       <c r="V34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W34">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>413</v>
       </c>
@@ -5061,8 +5271,14 @@
       <c r="V35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W35">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>417</v>
       </c>
@@ -5129,8 +5345,14 @@
       <c r="V36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W36">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>422</v>
       </c>
@@ -5197,8 +5419,14 @@
       <c r="V37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W37">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>427</v>
       </c>
@@ -5265,8 +5493,14 @@
       <c r="V38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W38">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>429</v>
       </c>
@@ -5333,8 +5567,14 @@
       <c r="V39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W39">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>439</v>
       </c>
@@ -5401,8 +5641,14 @@
       <c r="V40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W40">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>441</v>
       </c>
@@ -5469,8 +5715,14 @@
       <c r="V41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W41">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>442</v>
       </c>
@@ -5537,8 +5789,14 @@
       <c r="V42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W42">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>443</v>
       </c>
@@ -5605,8 +5863,14 @@
       <c r="V43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W43">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>444</v>
       </c>
@@ -5673,8 +5937,14 @@
       <c r="V44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W44">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>460</v>
       </c>
@@ -5741,8 +6011,14 @@
       <c r="V45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W45">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>485</v>
       </c>
@@ -5809,8 +6085,14 @@
       <c r="V46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W46">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>488</v>
       </c>
@@ -5877,8 +6159,14 @@
       <c r="V47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W47">
+        <v>1</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>515</v>
       </c>
@@ -5945,8 +6233,14 @@
       <c r="V48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W48">
+        <v>1</v>
+      </c>
+      <c r="X48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>522</v>
       </c>
@@ -6013,8 +6307,14 @@
       <c r="V49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W49">
+        <v>1</v>
+      </c>
+      <c r="X49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>530</v>
       </c>
@@ -6081,8 +6381,14 @@
       <c r="V50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W50">
+        <v>1</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>533</v>
       </c>
@@ -6149,8 +6455,14 @@
       <c r="V51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W51">
+        <v>1</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>536</v>
       </c>
@@ -6217,8 +6529,14 @@
       <c r="V52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W52">
+        <v>1</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>545</v>
       </c>
@@ -6285,8 +6603,14 @@
       <c r="V53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W53">
+        <v>1</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>566</v>
       </c>
@@ -6353,8 +6677,14 @@
       <c r="V54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>584</v>
       </c>
@@ -6421,8 +6751,14 @@
       <c r="V55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W55">
+        <v>1</v>
+      </c>
+      <c r="X55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>593</v>
       </c>
@@ -6489,8 +6825,14 @@
       <c r="V56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W56">
+        <v>1</v>
+      </c>
+      <c r="X56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>606</v>
       </c>
@@ -6557,8 +6899,14 @@
       <c r="V57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W57">
+        <v>1</v>
+      </c>
+      <c r="X57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>607</v>
       </c>
@@ -6625,8 +6973,14 @@
       <c r="V58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W58">
+        <v>1</v>
+      </c>
+      <c r="X58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>629</v>
       </c>
@@ -6693,8 +7047,14 @@
       <c r="V59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W59">
+        <v>1</v>
+      </c>
+      <c r="X59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>636</v>
       </c>
@@ -6761,8 +7121,14 @@
       <c r="V60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W60">
+        <v>1</v>
+      </c>
+      <c r="X60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>643</v>
       </c>
@@ -6829,8 +7195,14 @@
       <c r="V61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W61">
+        <v>1</v>
+      </c>
+      <c r="X61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>644</v>
       </c>
@@ -6897,8 +7269,14 @@
       <c r="V62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W62">
+        <v>1</v>
+      </c>
+      <c r="X62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>648</v>
       </c>
@@ -6965,8 +7343,14 @@
       <c r="V63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W63">
+        <v>1</v>
+      </c>
+      <c r="X63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>649</v>
       </c>
@@ -7033,8 +7417,14 @@
       <c r="V64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W64">
+        <v>1</v>
+      </c>
+      <c r="X64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>650</v>
       </c>
@@ -7101,8 +7491,14 @@
       <c r="V65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W65">
+        <v>1</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>684</v>
       </c>
@@ -7169,8 +7565,14 @@
       <c r="V66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W66">
+        <v>1</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>688</v>
       </c>
@@ -7237,8 +7639,14 @@
       <c r="V67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W67">
+        <v>1</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>692</v>
       </c>
@@ -7305,8 +7713,14 @@
       <c r="V68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W68">
+        <v>1</v>
+      </c>
+      <c r="X68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>693</v>
       </c>
@@ -7373,8 +7787,14 @@
       <c r="V69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W69">
+        <v>1</v>
+      </c>
+      <c r="X69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>707</v>
       </c>
@@ -7441,8 +7861,14 @@
       <c r="V70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W70">
+        <v>1</v>
+      </c>
+      <c r="X70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>718</v>
       </c>
@@ -7509,8 +7935,14 @@
       <c r="V71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W71">
+        <v>1</v>
+      </c>
+      <c r="X71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>725</v>
       </c>
@@ -7577,8 +8009,14 @@
       <c r="V72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W72">
+        <v>1</v>
+      </c>
+      <c r="X72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>753</v>
       </c>
@@ -7645,8 +8083,14 @@
       <c r="V73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W73">
+        <v>1</v>
+      </c>
+      <c r="X73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>754</v>
       </c>
@@ -7713,8 +8157,14 @@
       <c r="V74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W74">
+        <v>1</v>
+      </c>
+      <c r="X74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>757</v>
       </c>
@@ -7781,8 +8231,14 @@
       <c r="V75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W75">
+        <v>1</v>
+      </c>
+      <c r="X75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>758</v>
       </c>
@@ -7849,8 +8305,14 @@
       <c r="V76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W76">
+        <v>1</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>759</v>
       </c>
@@ -7917,8 +8379,14 @@
       <c r="V77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W77">
+        <v>1</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>764</v>
       </c>
@@ -7985,8 +8453,14 @@
       <c r="V78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W78">
+        <v>1</v>
+      </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>782</v>
       </c>
@@ -8053,8 +8527,14 @@
       <c r="V79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W79">
+        <v>1</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>783</v>
       </c>
@@ -8121,8 +8601,14 @@
       <c r="V80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W80">
+        <v>1</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>795</v>
       </c>
@@ -8189,8 +8675,14 @@
       <c r="V81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W81">
+        <v>1</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>800</v>
       </c>
@@ -8257,8 +8749,14 @@
       <c r="V82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W82">
+        <v>1</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>802</v>
       </c>
@@ -8325,8 +8823,14 @@
       <c r="V83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W83">
+        <v>1</v>
+      </c>
+      <c r="X83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>808</v>
       </c>
@@ -8393,8 +8897,14 @@
       <c r="V84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W84">
+        <v>1</v>
+      </c>
+      <c r="X84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>817</v>
       </c>
@@ -8461,8 +8971,14 @@
       <c r="V85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W85">
+        <v>1</v>
+      </c>
+      <c r="X85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>818</v>
       </c>
@@ -8529,8 +9045,14 @@
       <c r="V86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W86">
+        <v>1</v>
+      </c>
+      <c r="X86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>841</v>
       </c>
@@ -8597,8 +9119,14 @@
       <c r="V87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W87">
+        <v>1</v>
+      </c>
+      <c r="X87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>857</v>
       </c>
@@ -8665,8 +9193,14 @@
       <c r="V88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W88">
+        <v>1</v>
+      </c>
+      <c r="X88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>858</v>
       </c>
@@ -8733,8 +9267,14 @@
       <c r="V89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W89">
+        <v>1</v>
+      </c>
+      <c r="X89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>862</v>
       </c>
@@ -8801,8 +9341,14 @@
       <c r="V90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W90">
+        <v>1</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>865</v>
       </c>
@@ -8869,8 +9415,14 @@
       <c r="V91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W91">
+        <v>1</v>
+      </c>
+      <c r="X91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>885</v>
       </c>
@@ -8937,8 +9489,14 @@
       <c r="V92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W92">
+        <v>1</v>
+      </c>
+      <c r="X92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>891</v>
       </c>
@@ -9005,8 +9563,14 @@
       <c r="V93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W93">
+        <v>1</v>
+      </c>
+      <c r="X93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>893</v>
       </c>
@@ -9073,8 +9637,14 @@
       <c r="V94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W94">
+        <v>1</v>
+      </c>
+      <c r="X94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>894</v>
       </c>
@@ -9141,8 +9711,14 @@
       <c r="V95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W95">
+        <v>1</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>896</v>
       </c>
@@ -9209,8 +9785,14 @@
       <c r="V96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W96">
+        <v>1</v>
+      </c>
+      <c r="X96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>938</v>
       </c>
@@ -9277,8 +9859,14 @@
       <c r="V97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W97">
+        <v>1</v>
+      </c>
+      <c r="X97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>942</v>
       </c>
@@ -9345,8 +9933,14 @@
       <c r="V98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W98">
+        <v>1</v>
+      </c>
+      <c r="X98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>943</v>
       </c>
@@ -9413,8 +10007,14 @@
       <c r="V99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W99">
+        <v>1</v>
+      </c>
+      <c r="X99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>956</v>
       </c>
@@ -9481,8 +10081,14 @@
       <c r="V100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W100">
+        <v>1</v>
+      </c>
+      <c r="X100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>957</v>
       </c>
@@ -9549,8 +10155,14 @@
       <c r="V101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W101">
+        <v>1</v>
+      </c>
+      <c r="X101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>974</v>
       </c>
@@ -9617,8 +10229,14 @@
       <c r="V102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W102">
+        <v>1</v>
+      </c>
+      <c r="X102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>983</v>
       </c>
@@ -9685,8 +10303,14 @@
       <c r="V103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W103">
+        <v>1</v>
+      </c>
+      <c r="X103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>1023</v>
       </c>
@@ -9753,8 +10377,14 @@
       <c r="V104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W104">
+        <v>1</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>1034</v>
       </c>
@@ -9821,8 +10451,14 @@
       <c r="V105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W105">
+        <v>1</v>
+      </c>
+      <c r="X105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>1037</v>
       </c>
@@ -9889,8 +10525,14 @@
       <c r="V106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W106">
+        <v>1</v>
+      </c>
+      <c r="X106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>1041</v>
       </c>
@@ -9957,8 +10599,14 @@
       <c r="V107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W107">
+        <v>1</v>
+      </c>
+      <c r="X107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>1042</v>
       </c>
@@ -10025,8 +10673,14 @@
       <c r="V108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W108">
+        <v>1</v>
+      </c>
+      <c r="X108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>1045</v>
       </c>
@@ -10093,8 +10747,14 @@
       <c r="V109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W109">
+        <v>1</v>
+      </c>
+      <c r="X109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>1049</v>
       </c>
@@ -10161,8 +10821,14 @@
       <c r="V110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W110">
+        <v>1</v>
+      </c>
+      <c r="X110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>1050</v>
       </c>
@@ -10229,8 +10895,14 @@
       <c r="V111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W111">
+        <v>1</v>
+      </c>
+      <c r="X111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>1051</v>
       </c>
@@ -10297,8 +10969,14 @@
       <c r="V112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W112">
+        <v>1</v>
+      </c>
+      <c r="X112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>1057</v>
       </c>
@@ -10365,8 +11043,14 @@
       <c r="V113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W113">
+        <v>1</v>
+      </c>
+      <c r="X113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>1067</v>
       </c>
@@ -10433,8 +11117,14 @@
       <c r="V114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W114">
+        <v>1</v>
+      </c>
+      <c r="X114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>1077</v>
       </c>
@@ -10501,8 +11191,14 @@
       <c r="V115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W115">
+        <v>1</v>
+      </c>
+      <c r="X115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>1079</v>
       </c>
@@ -10569,8 +11265,14 @@
       <c r="V116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W116">
+        <v>1</v>
+      </c>
+      <c r="X116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>1082</v>
       </c>
@@ -10637,8 +11339,14 @@
       <c r="V117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W117">
+        <v>1</v>
+      </c>
+      <c r="X117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>1083</v>
       </c>
@@ -10705,8 +11413,14 @@
       <c r="V118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W118">
+        <v>1</v>
+      </c>
+      <c r="X118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>1090</v>
       </c>
@@ -10773,8 +11487,14 @@
       <c r="V119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W119">
+        <v>1</v>
+      </c>
+      <c r="X119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>2025</v>
       </c>
@@ -10841,8 +11561,14 @@
       <c r="V120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W120">
+        <v>1</v>
+      </c>
+      <c r="X120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>2059</v>
       </c>
@@ -10909,8 +11635,14 @@
       <c r="V121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W121">
+        <v>1</v>
+      </c>
+      <c r="X121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>2075</v>
       </c>
@@ -10977,8 +11709,14 @@
       <c r="V122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W122">
+        <v>1</v>
+      </c>
+      <c r="X122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>2083</v>
       </c>
@@ -11045,8 +11783,14 @@
       <c r="V123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W123">
+        <v>1</v>
+      </c>
+      <c r="X123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>2092</v>
       </c>
@@ -11113,8 +11857,14 @@
       <c r="V124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W124">
+        <v>1</v>
+      </c>
+      <c r="X124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>2114</v>
       </c>
@@ -11181,8 +11931,14 @@
       <c r="V125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W125">
+        <v>1</v>
+      </c>
+      <c r="X125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>2115</v>
       </c>
@@ -11249,8 +12005,14 @@
       <c r="V126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W126">
+        <v>1</v>
+      </c>
+      <c r="X126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>2121</v>
       </c>
@@ -11317,8 +12079,14 @@
       <c r="V127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W127">
+        <v>1</v>
+      </c>
+      <c r="X127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>2122</v>
       </c>
@@ -11385,8 +12153,14 @@
       <c r="V128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W128">
+        <v>1</v>
+      </c>
+      <c r="X128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>2123</v>
       </c>
@@ -11453,8 +12227,14 @@
       <c r="V129">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W129">
+        <v>1</v>
+      </c>
+      <c r="X129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>2124</v>
       </c>
@@ -11521,8 +12301,14 @@
       <c r="V130">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W130">
+        <v>1</v>
+      </c>
+      <c r="X130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>3101</v>
       </c>
@@ -11589,8 +12375,14 @@
       <c r="V131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W131">
+        <v>1</v>
+      </c>
+      <c r="X131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3104</v>
       </c>
@@ -11657,8 +12449,14 @@
       <c r="V132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W132">
+        <v>1</v>
+      </c>
+      <c r="X132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>3105</v>
       </c>
@@ -11725,8 +12523,14 @@
       <c r="V133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W133">
+        <v>1</v>
+      </c>
+      <c r="X133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>3600</v>
       </c>
@@ -11793,8 +12597,14 @@
       <c r="V134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W134">
+        <v>1</v>
+      </c>
+      <c r="X134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>3603</v>
       </c>
@@ -11861,8 +12671,14 @@
       <c r="V135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W135">
+        <v>1</v>
+      </c>
+      <c r="X135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>3604</v>
       </c>
@@ -11929,8 +12745,14 @@
       <c r="V136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W136">
+        <v>1</v>
+      </c>
+      <c r="X136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>3610</v>
       </c>
@@ -11997,8 +12819,14 @@
       <c r="V137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W137">
+        <v>1</v>
+      </c>
+      <c r="X137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>3615</v>
       </c>
@@ -12065,8 +12893,14 @@
       <c r="V138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W138">
+        <v>1</v>
+      </c>
+      <c r="X138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>3617</v>
       </c>
@@ -12133,8 +12967,14 @@
       <c r="V139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W139">
+        <v>1</v>
+      </c>
+      <c r="X139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>3622</v>
       </c>
@@ -12201,8 +13041,14 @@
       <c r="V140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W140">
+        <v>1</v>
+      </c>
+      <c r="X140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>4000</v>
       </c>
@@ -12269,8 +13115,14 @@
       <c r="V141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W141">
+        <v>1</v>
+      </c>
+      <c r="X141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>4006</v>
       </c>
@@ -12337,8 +13189,14 @@
       <c r="V142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W142">
+        <v>1</v>
+      </c>
+      <c r="X142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>4007</v>
       </c>
@@ -12405,8 +13263,14 @@
       <c r="V143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W143">
+        <v>1</v>
+      </c>
+      <c r="X143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>4008</v>
       </c>
@@ -12473,8 +13337,14 @@
       <c r="V144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W144">
+        <v>1</v>
+      </c>
+      <c r="X144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>4013</v>
       </c>
@@ -12541,8 +13411,14 @@
       <c r="V145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W145">
+        <v>1</v>
+      </c>
+      <c r="X145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>4014</v>
       </c>
@@ -12609,8 +13485,14 @@
       <c r="V146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W146">
+        <v>1</v>
+      </c>
+      <c r="X146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>4015</v>
       </c>
@@ -12677,8 +13559,14 @@
       <c r="V147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W147">
+        <v>1</v>
+      </c>
+      <c r="X147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>4016</v>
       </c>
@@ -12745,8 +13633,14 @@
       <c r="V148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W148">
+        <v>1</v>
+      </c>
+      <c r="X148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>4021</v>
       </c>
@@ -12813,8 +13707,14 @@
       <c r="V149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W149">
+        <v>1</v>
+      </c>
+      <c r="X149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>4057</v>
       </c>
@@ -12881,8 +13781,14 @@
       <c r="V150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W150">
+        <v>1</v>
+      </c>
+      <c r="X150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>4072</v>
       </c>
@@ -12949,8 +13855,14 @@
       <c r="V151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W151">
+        <v>1</v>
+      </c>
+      <c r="X151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>4073</v>
       </c>
@@ -13017,8 +13929,14 @@
       <c r="V152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W152">
+        <v>1</v>
+      </c>
+      <c r="X152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>4077</v>
       </c>
@@ -13085,8 +14003,14 @@
       <c r="V153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W153">
+        <v>1</v>
+      </c>
+      <c r="X153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>4080</v>
       </c>
@@ -13153,8 +14077,14 @@
       <c r="V154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W154">
+        <v>1</v>
+      </c>
+      <c r="X154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>4096</v>
       </c>
@@ -13221,8 +14151,14 @@
       <c r="V155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W155">
+        <v>1</v>
+      </c>
+      <c r="X155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>4104</v>
       </c>
@@ -13289,8 +14225,14 @@
       <c r="V156">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W156">
+        <v>1</v>
+      </c>
+      <c r="X156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>4111</v>
       </c>
@@ -13357,8 +14299,14 @@
       <c r="V157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W157">
+        <v>1</v>
+      </c>
+      <c r="X157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>4116</v>
       </c>
@@ -13425,8 +14373,14 @@
       <c r="V158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W158">
+        <v>1</v>
+      </c>
+      <c r="X158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>4119</v>
       </c>
@@ -13493,8 +14447,14 @@
       <c r="V159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W159">
+        <v>1</v>
+      </c>
+      <c r="X159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>4125</v>
       </c>
@@ -13561,8 +14521,14 @@
       <c r="V160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W160">
+        <v>1</v>
+      </c>
+      <c r="X160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>4126</v>
       </c>
@@ -13629,8 +14595,14 @@
       <c r="V161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W161">
+        <v>1</v>
+      </c>
+      <c r="X161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>4153</v>
       </c>
@@ -13697,8 +14669,14 @@
       <c r="V162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W162">
+        <v>1</v>
+      </c>
+      <c r="X162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>4162</v>
       </c>
@@ -13765,8 +14743,14 @@
       <c r="V163">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W163">
+        <v>1</v>
+      </c>
+      <c r="X163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>4163</v>
       </c>
@@ -13833,8 +14817,14 @@
       <c r="V164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W164">
+        <v>1</v>
+      </c>
+      <c r="X164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4164</v>
       </c>
@@ -13901,8 +14891,14 @@
       <c r="V165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W165">
+        <v>1</v>
+      </c>
+      <c r="X165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>4166</v>
       </c>
@@ -13969,8 +14965,14 @@
       <c r="V166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W166">
+        <v>1</v>
+      </c>
+      <c r="X166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>4169</v>
       </c>
@@ -14037,8 +15039,14 @@
       <c r="V167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W167">
+        <v>1</v>
+      </c>
+      <c r="X167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>4188</v>
       </c>
@@ -14105,8 +15113,14 @@
       <c r="V168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W168">
+        <v>1</v>
+      </c>
+      <c r="X168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>4198</v>
       </c>
@@ -14173,8 +15187,14 @@
       <c r="V169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W169">
+        <v>1</v>
+      </c>
+      <c r="X169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>4204</v>
       </c>
@@ -14241,8 +15261,14 @@
       <c r="V170">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W170">
+        <v>1</v>
+      </c>
+      <c r="X170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>4216</v>
       </c>
@@ -14309,8 +15335,14 @@
       <c r="V171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W171">
+        <v>1</v>
+      </c>
+      <c r="X171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>4220</v>
       </c>
@@ -14377,8 +15409,14 @@
       <c r="V172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W172">
+        <v>1</v>
+      </c>
+      <c r="X172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>4224</v>
       </c>
@@ -14445,8 +15483,14 @@
       <c r="V173">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W173">
+        <v>1</v>
+      </c>
+      <c r="X173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>4231</v>
       </c>
@@ -14513,8 +15557,14 @@
       <c r="V174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W174">
+        <v>1</v>
+      </c>
+      <c r="X174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>5002</v>
       </c>
@@ -14581,8 +15631,14 @@
       <c r="V175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W175">
+        <v>1</v>
+      </c>
+      <c r="X175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>5010</v>
       </c>
@@ -14649,8 +15705,14 @@
       <c r="V176">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W176">
+        <v>1</v>
+      </c>
+      <c r="X176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>5014</v>
       </c>
@@ -14717,8 +15779,14 @@
       <c r="V177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W177">
+        <v>1</v>
+      </c>
+      <c r="X177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>5016</v>
       </c>
@@ -14785,8 +15853,14 @@
       <c r="V178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W178">
+        <v>1</v>
+      </c>
+      <c r="X178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>5017</v>
       </c>
@@ -14853,8 +15927,14 @@
       <c r="V179">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W179">
+        <v>1</v>
+      </c>
+      <c r="X179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>5018</v>
       </c>
@@ -14921,8 +16001,14 @@
       <c r="V180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W180">
+        <v>1</v>
+      </c>
+      <c r="X180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>5019</v>
       </c>
@@ -14989,8 +16075,14 @@
       <c r="V181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W181">
+        <v>1</v>
+      </c>
+      <c r="X181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>5025</v>
       </c>
@@ -15057,8 +16149,14 @@
       <c r="V182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W182">
+        <v>1</v>
+      </c>
+      <c r="X182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>5027</v>
       </c>
@@ -15125,8 +16223,14 @@
       <c r="V183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W183">
+        <v>1</v>
+      </c>
+      <c r="X183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>5028</v>
       </c>
@@ -15193,8 +16297,14 @@
       <c r="V184">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W184">
+        <v>1</v>
+      </c>
+      <c r="X184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>5034</v>
       </c>
@@ -15261,8 +16371,14 @@
       <c r="V185">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W185">
+        <v>1</v>
+      </c>
+      <c r="X185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>5038</v>
       </c>
@@ -15329,8 +16445,14 @@
       <c r="V186">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W186">
+        <v>1</v>
+      </c>
+      <c r="X186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>5040</v>
       </c>
@@ -15397,8 +16519,14 @@
       <c r="V187">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W187">
+        <v>1</v>
+      </c>
+      <c r="X187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>5041</v>
       </c>
@@ -15465,8 +16593,14 @@
       <c r="V188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W188">
+        <v>1</v>
+      </c>
+      <c r="X188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>5048</v>
       </c>
@@ -15533,8 +16667,14 @@
       <c r="V189">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W189">
+        <v>1</v>
+      </c>
+      <c r="X189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>5052</v>
       </c>
@@ -15601,8 +16741,14 @@
       <c r="V190">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W190">
+        <v>1</v>
+      </c>
+      <c r="X190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>5053</v>
       </c>
@@ -15669,8 +16815,14 @@
       <c r="V191">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W191">
+        <v>1</v>
+      </c>
+      <c r="X191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>5060</v>
       </c>
@@ -15737,8 +16889,14 @@
       <c r="V192">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W192">
+        <v>1</v>
+      </c>
+      <c r="X192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>5067</v>
       </c>
@@ -15805,8 +16963,14 @@
       <c r="V193">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W193">
+        <v>1</v>
+      </c>
+      <c r="X193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>5069</v>
       </c>
@@ -15873,8 +17037,14 @@
       <c r="V194">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W194">
+        <v>1</v>
+      </c>
+      <c r="X194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>5074</v>
       </c>
@@ -15941,8 +17111,14 @@
       <c r="V195">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W195">
+        <v>1</v>
+      </c>
+      <c r="X195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>5076</v>
       </c>
@@ -16009,8 +17185,14 @@
       <c r="V196">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W196">
+        <v>1</v>
+      </c>
+      <c r="X196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>5077</v>
       </c>
@@ -16077,8 +17259,14 @@
       <c r="V197">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W197">
+        <v>1</v>
+      </c>
+      <c r="X197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5086</v>
       </c>
@@ -16145,8 +17333,14 @@
       <c r="V198">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W198">
+        <v>1</v>
+      </c>
+      <c r="X198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6002</v>
       </c>
@@ -16213,8 +17407,14 @@
       <c r="V199">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W199">
+        <v>1</v>
+      </c>
+      <c r="X199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>6016</v>
       </c>
@@ -16281,8 +17481,14 @@
       <c r="V200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W200">
+        <v>1</v>
+      </c>
+      <c r="X200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>6018</v>
       </c>
@@ -16349,8 +17555,14 @@
       <c r="V201">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W201">
+        <v>1</v>
+      </c>
+      <c r="X201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>6019</v>
       </c>
@@ -16417,8 +17629,14 @@
       <c r="V202">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W202">
+        <v>1</v>
+      </c>
+      <c r="X202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>6022</v>
       </c>
@@ -16485,8 +17703,14 @@
       <c r="V203">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W203">
+        <v>1</v>
+      </c>
+      <c r="X203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>6023</v>
       </c>
@@ -16553,8 +17777,14 @@
       <c r="V204">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W204">
+        <v>1</v>
+      </c>
+      <c r="X204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>6025</v>
       </c>
@@ -16621,8 +17851,14 @@
       <c r="V205">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W205">
+        <v>1</v>
+      </c>
+      <c r="X205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>6026</v>
       </c>
@@ -16689,8 +17925,14 @@
       <c r="V206">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W206">
+        <v>1</v>
+      </c>
+      <c r="X206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>6028</v>
       </c>
@@ -16757,8 +17999,14 @@
       <c r="V207">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W207">
+        <v>1</v>
+      </c>
+      <c r="X207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>6029</v>
       </c>
@@ -16825,8 +18073,14 @@
       <c r="V208">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W208">
+        <v>1</v>
+      </c>
+      <c r="X208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>6031</v>
       </c>
@@ -16893,8 +18147,14 @@
       <c r="V209">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W209">
+        <v>1</v>
+      </c>
+      <c r="X209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>6040</v>
       </c>
@@ -16961,8 +18221,14 @@
       <c r="V210">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W210">
+        <v>1</v>
+      </c>
+      <c r="X210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>6046</v>
       </c>
@@ -17029,8 +18295,14 @@
       <c r="V211">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W211">
+        <v>1</v>
+      </c>
+      <c r="X211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>6050</v>
       </c>
@@ -17097,8 +18369,14 @@
       <c r="V212">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W212">
+        <v>1</v>
+      </c>
+      <c r="X212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>6051</v>
       </c>
@@ -17165,8 +18443,14 @@
       <c r="V213">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W213">
+        <v>1</v>
+      </c>
+      <c r="X213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>6053</v>
       </c>
@@ -17233,8 +18517,14 @@
       <c r="V214">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W214">
+        <v>1</v>
+      </c>
+      <c r="X214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>6056</v>
       </c>
@@ -17301,8 +18591,14 @@
       <c r="V215">
         <v>0</v>
       </c>
-    </row>
-    <row r="216" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W215">
+        <v>1</v>
+      </c>
+      <c r="X215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>6060</v>
       </c>
@@ -17369,8 +18665,14 @@
       <c r="V216">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W216">
+        <v>1</v>
+      </c>
+      <c r="X216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>6062</v>
       </c>
@@ -17437,8 +18739,14 @@
       <c r="V217">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W217">
+        <v>1</v>
+      </c>
+      <c r="X217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>6063</v>
       </c>
@@ -17505,8 +18813,14 @@
       <c r="V218">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W218">
+        <v>1</v>
+      </c>
+      <c r="X218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>6064</v>
       </c>
@@ -17573,8 +18887,14 @@
       <c r="V219">
         <v>0</v>
       </c>
-    </row>
-    <row r="220" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W219">
+        <v>1</v>
+      </c>
+      <c r="X219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>6067</v>
       </c>
@@ -17641,8 +18961,14 @@
       <c r="V220">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W220">
+        <v>1</v>
+      </c>
+      <c r="X220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>6072</v>
       </c>
@@ -17709,8 +19035,14 @@
       <c r="V221">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W221">
+        <v>1</v>
+      </c>
+      <c r="X221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>6077</v>
       </c>
@@ -17777,8 +19109,14 @@
       <c r="V222">
         <v>0</v>
       </c>
-    </row>
-    <row r="223" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W222">
+        <v>1</v>
+      </c>
+      <c r="X222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>6081</v>
       </c>
@@ -17845,8 +19183,14 @@
       <c r="V223">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W223">
+        <v>1</v>
+      </c>
+      <c r="X223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>6083</v>
       </c>
@@ -17913,8 +19257,14 @@
       <c r="V224">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W224">
+        <v>1</v>
+      </c>
+      <c r="X224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>6084</v>
       </c>
@@ -17981,8 +19331,14 @@
       <c r="V225">
         <v>0</v>
       </c>
-    </row>
-    <row r="226" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W225">
+        <v>1</v>
+      </c>
+      <c r="X225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>6087</v>
       </c>
@@ -18049,8 +19405,14 @@
       <c r="V226">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W226">
+        <v>1</v>
+      </c>
+      <c r="X226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>6088</v>
       </c>
@@ -18117,8 +19479,14 @@
       <c r="V227">
         <v>1</v>
       </c>
-    </row>
-    <row r="228" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W227">
+        <v>1</v>
+      </c>
+      <c r="X227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>6089</v>
       </c>
@@ -18185,8 +19553,14 @@
       <c r="V228">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W228">
+        <v>1</v>
+      </c>
+      <c r="X228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>6091</v>
       </c>
@@ -18253,8 +19627,14 @@
       <c r="V229">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W229">
+        <v>1</v>
+      </c>
+      <c r="X229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>6092</v>
       </c>
@@ -18321,8 +19701,14 @@
       <c r="V230">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W230">
+        <v>1</v>
+      </c>
+      <c r="X230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6096</v>
       </c>
@@ -18389,8 +19775,14 @@
       <c r="V231">
         <v>0</v>
       </c>
-    </row>
-    <row r="232" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W231">
+        <v>1</v>
+      </c>
+      <c r="X231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>6097</v>
       </c>
@@ -18457,8 +19849,14 @@
       <c r="V232">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W232">
+        <v>1</v>
+      </c>
+      <c r="X232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>6100</v>
       </c>
@@ -18525,8 +19923,14 @@
       <c r="V233">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W233">
+        <v>1</v>
+      </c>
+      <c r="X233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>6101</v>
       </c>
@@ -18593,8 +19997,14 @@
       <c r="V234">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W234">
+        <v>1</v>
+      </c>
+      <c r="X234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>6102</v>
       </c>
@@ -18661,8 +20071,14 @@
       <c r="V235">
         <v>0</v>
       </c>
-    </row>
-    <row r="236" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W235">
+        <v>1</v>
+      </c>
+      <c r="X235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>6103</v>
       </c>
@@ -18729,8 +20145,14 @@
       <c r="V236">
         <v>0</v>
       </c>
-    </row>
-    <row r="237" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W236">
+        <v>1</v>
+      </c>
+      <c r="X236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>6104</v>
       </c>
@@ -18797,8 +20219,14 @@
       <c r="V237">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W237">
+        <v>1</v>
+      </c>
+      <c r="X237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>7003</v>
       </c>
@@ -18865,8 +20293,14 @@
       <c r="V238">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W238">
+        <v>1</v>
+      </c>
+      <c r="X238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>7009</v>
       </c>
@@ -18933,8 +20367,14 @@
       <c r="V239">
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W239">
+        <v>1</v>
+      </c>
+      <c r="X239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>7010</v>
       </c>
@@ -19001,8 +20441,14 @@
       <c r="V240">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W240">
+        <v>1</v>
+      </c>
+      <c r="X240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>7012</v>
       </c>
@@ -19069,8 +20515,14 @@
       <c r="V241">
         <v>1</v>
       </c>
-    </row>
-    <row r="242" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W241">
+        <v>1</v>
+      </c>
+      <c r="X241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>7014</v>
       </c>
@@ -19137,8 +20589,14 @@
       <c r="V242">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W242">
+        <v>1</v>
+      </c>
+      <c r="X242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>7029</v>
       </c>
@@ -19205,8 +20663,14 @@
       <c r="V243">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W243">
+        <v>1</v>
+      </c>
+      <c r="X243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>7031</v>
       </c>
@@ -19273,8 +20737,14 @@
       <c r="V244">
         <v>1</v>
       </c>
-    </row>
-    <row r="245" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W244">
+        <v>1</v>
+      </c>
+      <c r="X244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>7035</v>
       </c>
@@ -19341,8 +20811,14 @@
       <c r="V245">
         <v>1</v>
       </c>
-    </row>
-    <row r="246" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W245">
+        <v>1</v>
+      </c>
+      <c r="X245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>7038</v>
       </c>
@@ -19409,8 +20885,14 @@
       <c r="V246">
         <v>1</v>
       </c>
-    </row>
-    <row r="247" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W246">
+        <v>1</v>
+      </c>
+      <c r="X246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>7039</v>
       </c>
@@ -19477,8 +20959,14 @@
       <c r="V247">
         <v>1</v>
       </c>
-    </row>
-    <row r="248" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W247">
+        <v>1</v>
+      </c>
+      <c r="X247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>7040</v>
       </c>
@@ -19545,8 +21033,14 @@
       <c r="V248">
         <v>1</v>
       </c>
-    </row>
-    <row r="249" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W248">
+        <v>1</v>
+      </c>
+      <c r="X248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>7042</v>
       </c>
@@ -19613,8 +21107,14 @@
       <c r="V249">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W249">
+        <v>1</v>
+      </c>
+      <c r="X249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>7044</v>
       </c>
@@ -19681,8 +21181,14 @@
       <c r="V250">
         <v>1</v>
       </c>
-    </row>
-    <row r="251" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W250">
+        <v>1</v>
+      </c>
+      <c r="X250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>7048</v>
       </c>
@@ -19749,8 +21255,14 @@
       <c r="V251">
         <v>0</v>
       </c>
-    </row>
-    <row r="252" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W251">
+        <v>1</v>
+      </c>
+      <c r="X251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>7055</v>
       </c>
@@ -19817,8 +21329,14 @@
       <c r="V252">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W252">
+        <v>1</v>
+      </c>
+      <c r="X252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>7058</v>
       </c>
@@ -19885,8 +21403,14 @@
       <c r="V253">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W253">
+        <v>1</v>
+      </c>
+      <c r="X253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>7059</v>
       </c>
@@ -19953,8 +21477,14 @@
       <c r="V254">
         <v>1</v>
       </c>
-    </row>
-    <row r="255" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W254">
+        <v>1</v>
+      </c>
+      <c r="X254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>7061</v>
       </c>
@@ -20021,8 +21551,14 @@
       <c r="V255">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W255">
+        <v>1</v>
+      </c>
+      <c r="X255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>7066</v>
       </c>
@@ -20089,8 +21625,14 @@
       <c r="V256">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W256">
+        <v>1</v>
+      </c>
+      <c r="X256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>7067</v>
       </c>
@@ -20157,8 +21699,14 @@
       <c r="V257">
         <v>0</v>
       </c>
-    </row>
-    <row r="258" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W257">
+        <v>1</v>
+      </c>
+      <c r="X257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>7068</v>
       </c>
@@ -20225,8 +21773,14 @@
       <c r="V258">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W258">
+        <v>1</v>
+      </c>
+      <c r="X258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>7069</v>
       </c>
@@ -20293,8 +21847,14 @@
       <c r="V259">
         <v>1</v>
       </c>
-    </row>
-    <row r="260" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W259">
+        <v>1</v>
+      </c>
+      <c r="X259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>7077</v>
       </c>
@@ -20361,8 +21921,14 @@
       <c r="V260">
         <v>1</v>
       </c>
-    </row>
-    <row r="261" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W260">
+        <v>1</v>
+      </c>
+      <c r="X260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>7078</v>
       </c>
@@ -20429,8 +21995,14 @@
       <c r="V261">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W261">
+        <v>1</v>
+      </c>
+      <c r="X261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>7079</v>
       </c>
@@ -20497,8 +22069,14 @@
       <c r="V262">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W262">
+        <v>1</v>
+      </c>
+      <c r="X262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>7081</v>
       </c>
@@ -20565,8 +22143,14 @@
       <c r="V263">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W263">
+        <v>1</v>
+      </c>
+      <c r="X263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7083</v>
       </c>
@@ -20633,8 +22217,14 @@
       <c r="V264">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W264">
+        <v>1</v>
+      </c>
+      <c r="X264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>7084</v>
       </c>
@@ -20701,8 +22291,14 @@
       <c r="V265">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W265">
+        <v>1</v>
+      </c>
+      <c r="X265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>7086</v>
       </c>
@@ -20769,8 +22365,14 @@
       <c r="V266">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W266">
+        <v>1</v>
+      </c>
+      <c r="X266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>8004</v>
       </c>
@@ -20837,8 +22439,14 @@
       <c r="V267">
         <v>1</v>
       </c>
-    </row>
-    <row r="268" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W267">
+        <v>1</v>
+      </c>
+      <c r="X267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>8005</v>
       </c>
@@ -20905,8 +22513,14 @@
       <c r="V268">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W268">
+        <v>1</v>
+      </c>
+      <c r="X268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>8006</v>
       </c>
@@ -20973,8 +22587,14 @@
       <c r="V269">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W269">
+        <v>1</v>
+      </c>
+      <c r="X269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>8007</v>
       </c>
@@ -21041,8 +22661,14 @@
       <c r="V270">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W270">
+        <v>1</v>
+      </c>
+      <c r="X270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>8011</v>
       </c>
@@ -21109,8 +22735,14 @@
       <c r="V271">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W271">
+        <v>1</v>
+      </c>
+      <c r="X271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>8013</v>
       </c>
@@ -21177,8 +22809,14 @@
       <c r="V272">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W272">
+        <v>1</v>
+      </c>
+      <c r="X272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>8016</v>
       </c>
@@ -21245,8 +22883,14 @@
       <c r="V273">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W273">
+        <v>1</v>
+      </c>
+      <c r="X273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>8017</v>
       </c>
@@ -21313,8 +22957,14 @@
       <c r="V274">
         <v>1</v>
       </c>
-    </row>
-    <row r="275" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W274">
+        <v>1</v>
+      </c>
+      <c r="X274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>8021</v>
       </c>
@@ -21381,8 +23031,14 @@
       <c r="V275">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W275">
+        <v>1</v>
+      </c>
+      <c r="X275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>8022</v>
       </c>
@@ -21449,8 +23105,14 @@
       <c r="V276">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W276">
+        <v>1</v>
+      </c>
+      <c r="X276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>8029</v>
       </c>
@@ -21517,8 +23179,14 @@
       <c r="V277">
         <v>0</v>
       </c>
-    </row>
-    <row r="278" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W277">
+        <v>1</v>
+      </c>
+      <c r="X277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>8032</v>
       </c>
@@ -21585,8 +23253,14 @@
       <c r="V278">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W278">
+        <v>1</v>
+      </c>
+      <c r="X278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>8033</v>
       </c>
@@ -21653,8 +23327,14 @@
       <c r="V279">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W279">
+        <v>1</v>
+      </c>
+      <c r="X279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>8035</v>
       </c>
@@ -21721,8 +23401,14 @@
       <c r="V280">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W280">
+        <v>1</v>
+      </c>
+      <c r="X280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>8038</v>
       </c>
@@ -21789,8 +23475,14 @@
       <c r="V281">
         <v>1</v>
       </c>
-    </row>
-    <row r="282" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W281">
+        <v>1</v>
+      </c>
+      <c r="X281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>8042</v>
       </c>
@@ -21857,8 +23549,14 @@
       <c r="V282">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W282">
+        <v>1</v>
+      </c>
+      <c r="X282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>8043</v>
       </c>
@@ -21925,8 +23623,14 @@
       <c r="V283">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W283">
+        <v>1</v>
+      </c>
+      <c r="X283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>8046</v>
       </c>
@@ -21993,8 +23697,14 @@
       <c r="V284">
         <v>0</v>
       </c>
-    </row>
-    <row r="285" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W284">
+        <v>1</v>
+      </c>
+      <c r="X284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>8059</v>
       </c>
@@ -22061,8 +23771,14 @@
       <c r="V285">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W285">
+        <v>1</v>
+      </c>
+      <c r="X285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>8065</v>
       </c>
@@ -22129,8 +23845,14 @@
       <c r="V286">
         <v>1</v>
       </c>
-    </row>
-    <row r="287" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W286">
+        <v>1</v>
+      </c>
+      <c r="X286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>8066</v>
       </c>
@@ -22197,8 +23919,14 @@
       <c r="V287">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W287">
+        <v>1</v>
+      </c>
+      <c r="X287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>8068</v>
       </c>
@@ -22265,8 +23993,14 @@
       <c r="V288">
         <v>1</v>
       </c>
-    </row>
-    <row r="289" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W288">
+        <v>1</v>
+      </c>
+      <c r="X288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>8069</v>
       </c>
@@ -22333,8 +24067,14 @@
       <c r="V289">
         <v>1</v>
       </c>
-    </row>
-    <row r="290" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W289">
+        <v>1</v>
+      </c>
+      <c r="X289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>8070</v>
       </c>
@@ -22401,8 +24141,14 @@
       <c r="V290">
         <v>1</v>
       </c>
-    </row>
-    <row r="291" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W290">
+        <v>1</v>
+      </c>
+      <c r="X290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>8071</v>
       </c>
@@ -22469,8 +24215,14 @@
       <c r="V291">
         <v>1</v>
       </c>
-    </row>
-    <row r="292" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W291">
+        <v>1</v>
+      </c>
+      <c r="X291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>8075</v>
       </c>
@@ -22537,8 +24289,14 @@
       <c r="V292">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W292">
+        <v>1</v>
+      </c>
+      <c r="X292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>8076</v>
       </c>
@@ -22605,8 +24363,14 @@
       <c r="V293">
         <v>0</v>
       </c>
-    </row>
-    <row r="294" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W293">
+        <v>1</v>
+      </c>
+      <c r="X293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>8077</v>
       </c>
@@ -22673,8 +24437,14 @@
       <c r="V294">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W294">
+        <v>1</v>
+      </c>
+      <c r="X294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>8078</v>
       </c>
@@ -22741,8 +24511,14 @@
       <c r="V295">
         <v>0</v>
       </c>
-    </row>
-    <row r="296" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W295">
+        <v>1</v>
+      </c>
+      <c r="X295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>8084</v>
       </c>
@@ -22809,8 +24585,14 @@
       <c r="V296">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W296">
+        <v>1</v>
+      </c>
+      <c r="X296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8088</v>
       </c>
@@ -22877,8 +24659,14 @@
       <c r="V297">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W297">
+        <v>1</v>
+      </c>
+      <c r="X297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>8092</v>
       </c>
@@ -22945,8 +24733,14 @@
       <c r="V298">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W298">
+        <v>1</v>
+      </c>
+      <c r="X298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>8093</v>
       </c>
@@ -23013,8 +24807,14 @@
       <c r="V299">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W299">
+        <v>1</v>
+      </c>
+      <c r="X299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>8094</v>
       </c>
@@ -23081,8 +24881,14 @@
       <c r="V300">
         <v>1</v>
       </c>
-    </row>
-    <row r="301" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W300">
+        <v>1</v>
+      </c>
+      <c r="X300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>8095</v>
       </c>
@@ -23149,8 +24955,14 @@
       <c r="V301">
         <v>0</v>
       </c>
-    </row>
-    <row r="302" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W301">
+        <v>1</v>
+      </c>
+      <c r="X301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>8106</v>
       </c>
@@ -23217,8 +25029,14 @@
       <c r="V302">
         <v>0</v>
       </c>
-    </row>
-    <row r="303" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W302">
+        <v>1</v>
+      </c>
+      <c r="X302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>8107</v>
       </c>
@@ -23285,8 +25103,14 @@
       <c r="V303">
         <v>0</v>
       </c>
-    </row>
-    <row r="304" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W303">
+        <v>1</v>
+      </c>
+      <c r="X303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>8108</v>
       </c>
@@ -23353,8 +25177,14 @@
       <c r="V304">
         <v>0</v>
       </c>
-    </row>
-    <row r="305" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W304">
+        <v>1</v>
+      </c>
+      <c r="X304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>8115</v>
       </c>
@@ -23421,8 +25251,14 @@
       <c r="V305">
         <v>0</v>
       </c>
-    </row>
-    <row r="306" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W305">
+        <v>1</v>
+      </c>
+      <c r="X305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>8130</v>
       </c>
@@ -23489,8 +25325,14 @@
       <c r="V306">
         <v>0</v>
       </c>
-    </row>
-    <row r="307" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W306">
+        <v>1</v>
+      </c>
+      <c r="X306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>8131</v>
       </c>
@@ -23557,8 +25399,14 @@
       <c r="V307">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W307">
+        <v>1</v>
+      </c>
+      <c r="X307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>8132</v>
       </c>
@@ -23625,8 +25473,14 @@
       <c r="V308">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W308">
+        <v>1</v>
+      </c>
+      <c r="X308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>8133</v>
       </c>
@@ -23693,8 +25547,14 @@
       <c r="V309">
         <v>0</v>
       </c>
-    </row>
-    <row r="310" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W309">
+        <v>1</v>
+      </c>
+      <c r="X309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>8134</v>
       </c>
@@ -23761,8 +25621,14 @@
       <c r="V310">
         <v>0</v>
       </c>
-    </row>
-    <row r="311" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W310">
+        <v>1</v>
+      </c>
+      <c r="X310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>8135</v>
       </c>
@@ -23829,8 +25695,14 @@
       <c r="V311">
         <v>0</v>
       </c>
-    </row>
-    <row r="312" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W311">
+        <v>1</v>
+      </c>
+      <c r="X311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>8136</v>
       </c>
@@ -23897,8 +25769,14 @@
       <c r="V312">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W312">
+        <v>1</v>
+      </c>
+      <c r="X312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>8137</v>
       </c>
@@ -23965,8 +25843,14 @@
       <c r="V313">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W313">
+        <v>1</v>
+      </c>
+      <c r="X313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>8144</v>
       </c>
@@ -24033,8 +25917,14 @@
       <c r="V314">
         <v>0</v>
       </c>
-    </row>
-    <row r="315" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W314">
+        <v>1</v>
+      </c>
+      <c r="X314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>8169</v>
       </c>
@@ -24101,8 +25991,14 @@
       <c r="V315">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W315">
+        <v>1</v>
+      </c>
+      <c r="X315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>8170</v>
       </c>
@@ -24169,8 +26065,14 @@
       <c r="V316">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W316">
+        <v>1</v>
+      </c>
+      <c r="X316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>8171</v>
       </c>
@@ -24237,8 +26139,14 @@
       <c r="V317">
         <v>0</v>
       </c>
-    </row>
-    <row r="318" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W317">
+        <v>1</v>
+      </c>
+      <c r="X317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>8172</v>
       </c>
@@ -24305,8 +26213,14 @@
       <c r="V318">
         <v>0</v>
       </c>
-    </row>
-    <row r="319" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W318">
+        <v>1</v>
+      </c>
+      <c r="X318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>8173</v>
       </c>
@@ -24373,8 +26287,14 @@
       <c r="V319">
         <v>0</v>
       </c>
-    </row>
-    <row r="320" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W319">
+        <v>1</v>
+      </c>
+      <c r="X319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>8174</v>
       </c>
@@ -24441,8 +26361,14 @@
       <c r="V320">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W320">
+        <v>1</v>
+      </c>
+      <c r="X320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>8175</v>
       </c>
@@ -24509,8 +26435,14 @@
       <c r="V321">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W321">
+        <v>1</v>
+      </c>
+      <c r="X321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>8176</v>
       </c>
@@ -24577,8 +26509,14 @@
       <c r="V322">
         <v>0</v>
       </c>
-    </row>
-    <row r="323" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W322">
+        <v>1</v>
+      </c>
+      <c r="X322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>8177</v>
       </c>
@@ -24645,8 +26583,14 @@
       <c r="V323">
         <v>0</v>
       </c>
-    </row>
-    <row r="324" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W323">
+        <v>1</v>
+      </c>
+      <c r="X323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>8178</v>
       </c>
@@ -24713,8 +26657,14 @@
       <c r="V324">
         <v>0</v>
       </c>
-    </row>
-    <row r="325" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W324">
+        <v>1</v>
+      </c>
+      <c r="X324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>8186</v>
       </c>
@@ -24781,8 +26731,14 @@
       <c r="V325">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W325">
+        <v>1</v>
+      </c>
+      <c r="X325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>8187</v>
       </c>
@@ -24849,8 +26805,14 @@
       <c r="V326">
         <v>0</v>
       </c>
-    </row>
-    <row r="327" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W326">
+        <v>1</v>
+      </c>
+      <c r="X326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>8188</v>
       </c>
@@ -24917,8 +26879,14 @@
       <c r="V327">
         <v>0</v>
       </c>
-    </row>
-    <row r="328" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W327">
+        <v>1</v>
+      </c>
+      <c r="X327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>8189</v>
       </c>
@@ -24985,8 +26953,14 @@
       <c r="V328">
         <v>0</v>
       </c>
-    </row>
-    <row r="329" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W328">
+        <v>1</v>
+      </c>
+      <c r="X328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8190</v>
       </c>
@@ -25053,8 +27027,14 @@
       <c r="V329">
         <v>0</v>
       </c>
-    </row>
-    <row r="330" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W329">
+        <v>1</v>
+      </c>
+      <c r="X329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>8194</v>
       </c>
@@ -25121,8 +27101,14 @@
       <c r="V330">
         <v>0</v>
       </c>
-    </row>
-    <row r="331" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W330">
+        <v>1</v>
+      </c>
+      <c r="X330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>8195</v>
       </c>
@@ -25189,8 +27175,14 @@
       <c r="V331">
         <v>0</v>
       </c>
-    </row>
-    <row r="332" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W331">
+        <v>1</v>
+      </c>
+      <c r="X331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>8196</v>
       </c>
@@ -25257,8 +27249,14 @@
       <c r="V332">
         <v>0</v>
       </c>
-    </row>
-    <row r="333" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W332">
+        <v>1</v>
+      </c>
+      <c r="X332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>8197</v>
       </c>
@@ -25325,8 +27323,14 @@
       <c r="V333">
         <v>0</v>
       </c>
-    </row>
-    <row r="334" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W333">
+        <v>1</v>
+      </c>
+      <c r="X333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>8198</v>
       </c>
@@ -25393,8 +27397,14 @@
       <c r="V334">
         <v>0</v>
       </c>
-    </row>
-    <row r="335" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W334">
+        <v>1</v>
+      </c>
+      <c r="X334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>8199</v>
       </c>
@@ -25461,8 +27471,14 @@
       <c r="V335">
         <v>0</v>
       </c>
-    </row>
-    <row r="336" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W335">
+        <v>1</v>
+      </c>
+      <c r="X335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>8200</v>
       </c>
@@ -25529,8 +27545,14 @@
       <c r="V336">
         <v>0</v>
       </c>
-    </row>
-    <row r="337" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W336">
+        <v>1</v>
+      </c>
+      <c r="X336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>8201</v>
       </c>
@@ -25597,8 +27619,14 @@
       <c r="V337">
         <v>0</v>
       </c>
-    </row>
-    <row r="338" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W337">
+        <v>1</v>
+      </c>
+      <c r="X337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>8202</v>
       </c>
@@ -25665,8 +27693,14 @@
       <c r="V338">
         <v>0</v>
       </c>
-    </row>
-    <row r="339" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W338">
+        <v>1</v>
+      </c>
+      <c r="X338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>8211</v>
       </c>
@@ -25733,8 +27767,14 @@
       <c r="V339">
         <v>1</v>
       </c>
-    </row>
-    <row r="340" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W339">
+        <v>1</v>
+      </c>
+      <c r="X339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>8212</v>
       </c>
@@ -25801,8 +27841,14 @@
       <c r="V340">
         <v>1</v>
       </c>
-    </row>
-    <row r="341" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W340">
+        <v>1</v>
+      </c>
+      <c r="X340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>8215</v>
       </c>
@@ -25869,8 +27915,14 @@
       <c r="V341">
         <v>1</v>
       </c>
-    </row>
-    <row r="342" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W341">
+        <v>1</v>
+      </c>
+      <c r="X341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>8221</v>
       </c>
@@ -25937,8 +27989,14 @@
       <c r="V342">
         <v>0</v>
       </c>
-    </row>
-    <row r="343" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W342">
+        <v>1</v>
+      </c>
+      <c r="X342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>8244</v>
       </c>
@@ -26005,8 +28063,14 @@
       <c r="V343">
         <v>0</v>
       </c>
-    </row>
-    <row r="344" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W343">
+        <v>1</v>
+      </c>
+      <c r="X343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>8256</v>
       </c>
@@ -26073,8 +28137,14 @@
       <c r="V344">
         <v>0</v>
       </c>
-    </row>
-    <row r="345" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W344">
+        <v>1</v>
+      </c>
+      <c r="X344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>8259</v>
       </c>
@@ -26141,8 +28211,14 @@
       <c r="V345">
         <v>0</v>
       </c>
-    </row>
-    <row r="346" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W345">
+        <v>1</v>
+      </c>
+      <c r="X345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>8266</v>
       </c>
@@ -26209,8 +28285,14 @@
       <c r="V346">
         <v>0</v>
       </c>
-    </row>
-    <row r="347" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W346">
+        <v>1</v>
+      </c>
+      <c r="X346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>8268</v>
       </c>
@@ -26277,8 +28359,14 @@
       <c r="V347">
         <v>0</v>
       </c>
-    </row>
-    <row r="348" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W347">
+        <v>1</v>
+      </c>
+      <c r="X347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>8271</v>
       </c>
@@ -26345,8 +28433,14 @@
       <c r="V348">
         <v>0</v>
       </c>
-    </row>
-    <row r="349" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W348">
+        <v>1</v>
+      </c>
+      <c r="X348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>8295</v>
       </c>
@@ -26413,8 +28507,14 @@
       <c r="V349">
         <v>0</v>
       </c>
-    </row>
-    <row r="350" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W349">
+        <v>1</v>
+      </c>
+      <c r="X349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>8306</v>
       </c>
@@ -26481,8 +28581,14 @@
       <c r="V350">
         <v>0</v>
       </c>
-    </row>
-    <row r="351" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W350">
+        <v>1</v>
+      </c>
+      <c r="X350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>8307</v>
       </c>
@@ -26549,8 +28655,14 @@
       <c r="V351">
         <v>1</v>
       </c>
-    </row>
-    <row r="352" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W351">
+        <v>1</v>
+      </c>
+      <c r="X351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>8308</v>
       </c>
@@ -26617,8 +28729,14 @@
       <c r="V352">
         <v>1</v>
       </c>
-    </row>
-    <row r="353" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W352">
+        <v>1</v>
+      </c>
+      <c r="X352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>8309</v>
       </c>
@@ -26685,8 +28803,14 @@
       <c r="V353">
         <v>0</v>
       </c>
-    </row>
-    <row r="354" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W353">
+        <v>1</v>
+      </c>
+      <c r="X353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>8310</v>
       </c>
@@ -26753,8 +28877,14 @@
       <c r="V354">
         <v>0</v>
       </c>
-    </row>
-    <row r="355" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W354">
+        <v>1</v>
+      </c>
+      <c r="X354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>8319</v>
       </c>
@@ -26821,8 +28951,14 @@
       <c r="V355">
         <v>1</v>
       </c>
-    </row>
-    <row r="356" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W355">
+        <v>1</v>
+      </c>
+      <c r="X355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>8322</v>
       </c>
@@ -26889,8 +29025,14 @@
       <c r="V356">
         <v>0</v>
       </c>
-    </row>
-    <row r="357" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W356">
+        <v>1</v>
+      </c>
+      <c r="X356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>8323</v>
       </c>
@@ -26957,8 +29099,14 @@
       <c r="V357">
         <v>0</v>
       </c>
-    </row>
-    <row r="358" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W357">
+        <v>1</v>
+      </c>
+      <c r="X357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>8324</v>
       </c>
@@ -27025,8 +29173,14 @@
       <c r="V358">
         <v>0</v>
       </c>
-    </row>
-    <row r="359" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W358">
+        <v>1</v>
+      </c>
+      <c r="X358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>8325</v>
       </c>
@@ -27093,8 +29247,14 @@
       <c r="V359">
         <v>0</v>
       </c>
-    </row>
-    <row r="360" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W359">
+        <v>1</v>
+      </c>
+      <c r="X359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>8326</v>
       </c>
@@ -27161,8 +29321,14 @@
       <c r="V360">
         <v>0</v>
       </c>
-    </row>
-    <row r="361" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W360">
+        <v>1</v>
+      </c>
+      <c r="X360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8330</v>
       </c>
@@ -27229,8 +29395,14 @@
       <c r="V361">
         <v>1</v>
       </c>
-    </row>
-    <row r="362" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W361">
+        <v>1</v>
+      </c>
+      <c r="X361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>8331</v>
       </c>
@@ -27297,8 +29469,14 @@
       <c r="V362">
         <v>0</v>
       </c>
-    </row>
-    <row r="363" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W362">
+        <v>1</v>
+      </c>
+      <c r="X362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>9997</v>
       </c>
@@ -27365,8 +29543,14 @@
       <c r="V363">
         <v>0</v>
       </c>
-    </row>
-    <row r="364" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W363">
+        <v>1</v>
+      </c>
+      <c r="X363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>9998</v>
       </c>
@@ -27433,8 +29617,14 @@
       <c r="V364">
         <v>0</v>
       </c>
-    </row>
-    <row r="365" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W364">
+        <v>1</v>
+      </c>
+      <c r="X364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>9999</v>
       </c>
@@ -27500,6 +29690,12 @@
       </c>
       <c r="V365">
         <v>0</v>
+      </c>
+      <c r="W365">
+        <v>1</v>
+      </c>
+      <c r="X365">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -27517,6 +29713,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cd15c362-78d0-46e3-855d-450aec0345ae">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="919db50e-9b93-4aa7-8f4d-aba87c2cfe80" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003BD54FBCA06F694A882683D7ACFDA923" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="654d623470b4a6fb6721727d56430b4d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cd15c362-78d0-46e3-855d-450aec0345ae" xmlns:ns3="919db50e-9b93-4aa7-8f4d-aba87c2cfe80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a32782979afd25915a6e5b9a8d07914c" ns2:_="" ns3:_="">
     <xsd:import namespace="cd15c362-78d0-46e3-855d-450aec0345ae"/>
@@ -27765,17 +29972,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cd15c362-78d0-46e3-855d-450aec0345ae">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="919db50e-9b93-4aa7-8f4d-aba87c2cfe80" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{203DE4BB-EA3C-4DDE-BD14-E491FBCB4234}">
   <ds:schemaRefs>
@@ -27785,6 +29981,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01F7C088-D178-46A6-8ED8-7DE77DCF1D21}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cd15c362-78d0-46e3-855d-450aec0345ae"/>
+    <ds:schemaRef ds:uri="919db50e-9b93-4aa7-8f4d-aba87c2cfe80"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC18504-9E98-46FD-A6B5-F8D478095409}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27801,15 +30008,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01F7C088-D178-46A6-8ED8-7DE77DCF1D21}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cd15c362-78d0-46e3-855d-450aec0345ae"/>
-    <ds:schemaRef ds:uri="919db50e-9b93-4aa7-8f4d-aba87c2cfe80"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>